--- a/HISPEC_allsubs.xlsx
+++ b/HISPEC_allsubs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashbake/Documents/Research/Projects/HISPEC/Throughput_Budget/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleybaker/Documents/HISPEC/ThroughputBudget/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36AB68F8-8A7A-F941-AC8F-0CFEC1628944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54855378-8521-C64D-8085-3D2C204EB6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18900" windowWidth="22400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7940" yWindow="-20400" windowWidth="22400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="185">
   <si>
     <t>Include?</t>
   </si>
@@ -212,15 +212,9 @@
     <t>Cold Stop</t>
   </si>
   <si>
-    <t>Echelle</t>
-  </si>
-  <si>
     <t>Cross Disperser</t>
   </si>
   <si>
-    <t>grating\echelle_canon.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">COL 1 </t>
   </si>
   <si>
@@ -509,12 +503,6 @@
     <t>Echelle Margin</t>
   </si>
   <si>
-    <t>The raw data arent well sampled and orders shifted so we took another curve and made the throughput match * 95% for margin</t>
-  </si>
-  <si>
-    <t>margin is in the raw file for now until get better data from canon</t>
-  </si>
-  <si>
     <t>grating\cx_bspec.csv</t>
   </si>
   <si>
@@ -533,18 +521,12 @@
     <t>from canon, RCWA</t>
   </si>
   <si>
-    <t>From canon - RCWA</t>
-  </si>
-  <si>
     <t>CX Margin</t>
   </si>
   <si>
     <t>margin</t>
   </si>
   <si>
-    <t xml:space="preserve">margin  </t>
-  </si>
-  <si>
     <t>Considers four connections, 0.97 each</t>
   </si>
   <si>
@@ -609,13 +591,37 @@
   </si>
   <si>
     <t>\coatings\Asahi\Theoretical\Transmission model(HISPEC FEI blocking filter_IR grade fused silica)-f6_0deg.csv</t>
+  </si>
+  <si>
+    <t>Echelle No Blaze</t>
+  </si>
+  <si>
+    <t>grating\echelle_noblaze.csv</t>
+  </si>
+  <si>
+    <t>no blaze included, *make sure to not double include the echelle here*</t>
+  </si>
+  <si>
+    <t>Blaze Curve</t>
+  </si>
+  <si>
+    <t>grating\echelle_blazeonly.csv</t>
+  </si>
+  <si>
+    <t>Blaze, doesn’t match HISPEC's exactly, just a stand in</t>
+  </si>
+  <si>
+    <t>From canon RCWA</t>
+  </si>
+  <si>
+    <t>no blaze included</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -657,6 +663,12 @@
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -791,7 +803,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -841,6 +853,10 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2024,7 +2040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5" style="2" customWidth="1"/>
@@ -2073,7 +2089,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2089,14 +2105,14 @@
         <v>9</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D3" s="28" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="29"/>
       <c r="F3" s="28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G3" s="28" t="s">
         <v>11</v>
@@ -2113,20 +2129,20 @@
         <v>9</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D4" s="28" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="29"/>
       <c r="F4" s="28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4" s="28" t="s">
         <v>11</v>
       </c>
       <c r="H4" s="28" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="30" customFormat="1" x14ac:dyDescent="0.25">
@@ -2137,14 +2153,14 @@
         <v>9</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D5" s="28" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="29"/>
       <c r="F5" s="28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G5" s="28" t="s">
         <v>11</v>
@@ -2205,7 +2221,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -2268,7 +2284,7 @@
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G11" s="28"/>
       <c r="H11" s="28"/>
@@ -2348,7 +2364,7 @@
       </c>
       <c r="E15" s="29"/>
       <c r="F15" s="28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G15" s="28"/>
       <c r="H15" s="28"/>
@@ -2388,7 +2404,7 @@
       </c>
       <c r="E17" s="29"/>
       <c r="F17" s="28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G17" s="28"/>
       <c r="H17" s="28"/>
@@ -2428,7 +2444,7 @@
       </c>
       <c r="E19" s="29"/>
       <c r="F19" s="28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G19" s="28"/>
       <c r="H19" s="28"/>
@@ -2468,7 +2484,7 @@
       </c>
       <c r="E21" s="29"/>
       <c r="F21" s="28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G21" s="28"/>
       <c r="H21" s="28"/>
@@ -2581,7 +2597,7 @@
         <v>8</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="13"/>
@@ -2606,7 +2622,7 @@
       <c r="F28" s="29"/>
       <c r="G28" s="29"/>
       <c r="H28" s="29" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="30" customFormat="1" x14ac:dyDescent="0.25">
@@ -2624,7 +2640,7 @@
       </c>
       <c r="E29" s="29"/>
       <c r="F29" s="29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G29" s="29" t="s">
         <v>35</v>
@@ -2646,13 +2662,13 @@
       </c>
       <c r="E30" s="29"/>
       <c r="F30" s="29" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G30" s="29" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="30" customFormat="1" x14ac:dyDescent="0.25">
@@ -2663,18 +2679,18 @@
         <v>9</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D31" s="31" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="29"/>
       <c r="F31" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G31" s="29"/>
       <c r="H31" s="29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="30" customFormat="1" x14ac:dyDescent="0.25">
@@ -2682,21 +2698,21 @@
         <v>1</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D32" s="31">
         <v>4</v>
       </c>
       <c r="E32" s="29"/>
       <c r="F32" s="29" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G32" s="29"/>
       <c r="H32" s="30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="30" customFormat="1" x14ac:dyDescent="0.25">
@@ -2707,18 +2723,18 @@
         <v>9</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D33" s="31" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="29"/>
       <c r="F33" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G33" s="29"/>
       <c r="H33" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="30" customFormat="1" x14ac:dyDescent="0.25">
@@ -2729,14 +2745,14 @@
         <v>9</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D34" s="44" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="43"/>
       <c r="F34" s="43" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G34" s="43"/>
       <c r="H34" s="43"/>
@@ -2746,17 +2762,17 @@
         <v>1</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D35" s="31">
         <v>4</v>
       </c>
       <c r="E35" s="29"/>
       <c r="F35" s="29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G35" s="29"/>
       <c r="H35" s="29"/>
@@ -2769,14 +2785,14 @@
         <v>9</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D36" s="44" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="43"/>
       <c r="F36" s="43" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G36" s="43"/>
       <c r="H36" s="43"/>
@@ -2789,18 +2805,18 @@
         <v>9</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D37" s="31" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="29"/>
       <c r="F37" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G37" s="29"/>
       <c r="H37" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="30" customFormat="1" x14ac:dyDescent="0.25">
@@ -2808,17 +2824,17 @@
         <v>1</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D38" s="31">
         <v>4</v>
       </c>
       <c r="E38" s="29"/>
       <c r="F38" s="29" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G38" s="29"/>
       <c r="H38" s="29"/>
@@ -2831,14 +2847,14 @@
         <v>9</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D39" s="31" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="29"/>
       <c r="F39" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G39" s="29"/>
       <c r="H39" s="29"/>
@@ -2851,14 +2867,14 @@
         <v>9</v>
       </c>
       <c r="C40" s="42" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D40" s="44" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="43"/>
       <c r="F40" s="43" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G40" s="43"/>
       <c r="H40" s="43"/>
@@ -2868,17 +2884,17 @@
         <v>1</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D41" s="31">
         <v>4</v>
       </c>
       <c r="E41" s="29"/>
       <c r="F41" s="29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G41" s="29"/>
       <c r="H41" s="29"/>
@@ -2891,14 +2907,14 @@
         <v>9</v>
       </c>
       <c r="C42" s="42" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D42" s="44" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="43"/>
       <c r="F42" s="43" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G42" s="43"/>
       <c r="H42" s="43"/>
@@ -2918,7 +2934,7 @@
       </c>
       <c r="E43" s="29"/>
       <c r="F43" s="29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G43" s="29" t="s">
         <v>35</v>
@@ -2933,7 +2949,7 @@
         <v>8</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="6"/>
@@ -2949,14 +2965,14 @@
         <v>9</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D45" s="37" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="16" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G45" s="16"/>
       <c r="H45" s="16"/>
@@ -2969,7 +2985,7 @@
         <v>12</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D46" s="15">
         <v>1</v>
@@ -2978,7 +2994,7 @@
       <c r="F46" s="16"/>
       <c r="G46" s="16"/>
       <c r="H46" s="16" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -2998,7 +3014,7 @@
       <c r="F47" s="16"/>
       <c r="G47" s="16"/>
       <c r="H47" s="16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -3018,7 +3034,7 @@
       <c r="F48" s="16"/>
       <c r="G48" s="16"/>
       <c r="H48" s="16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -3029,20 +3045,20 @@
         <v>9</v>
       </c>
       <c r="C49" s="47" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D49" s="48" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="17"/>
       <c r="F49" s="18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H49" s="47" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -3053,18 +3069,18 @@
         <v>9</v>
       </c>
       <c r="C50" s="45" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D50" s="46" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="17"/>
       <c r="F50" s="16" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G50" s="16"/>
       <c r="H50" s="16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -3084,7 +3100,7 @@
       <c r="F51" s="16"/>
       <c r="G51" s="16"/>
       <c r="H51" s="16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -3095,7 +3111,7 @@
         <v>8</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
@@ -3111,14 +3127,14 @@
         <v>9</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="11"/>
       <c r="F53" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G53" s="11"/>
       <c r="H53" s="10"/>
@@ -3131,14 +3147,14 @@
         <v>9</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="10" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G54" s="11"/>
       <c r="H54" s="10"/>
@@ -3151,18 +3167,18 @@
         <v>9</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="8" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -3182,7 +3198,7 @@
       <c r="F56" s="8"/>
       <c r="G56" s="11"/>
       <c r="H56" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -3193,18 +3209,18 @@
         <v>9</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -3215,18 +3231,18 @@
         <v>9</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G58" s="11"/>
       <c r="H58" s="11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -3237,14 +3253,14 @@
         <v>9</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="11"/>
       <c r="F59" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G59" s="11"/>
       <c r="H59" s="11"/>
@@ -3257,14 +3273,14 @@
         <v>9</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="11"/>
       <c r="F60" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G60" s="11"/>
       <c r="H60" s="11"/>
@@ -3277,7 +3293,7 @@
         <v>12</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D61" s="7">
         <f>1-0.0035</f>
@@ -3293,17 +3309,17 @@
         <v>1</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D62" s="7">
         <v>10</v>
       </c>
       <c r="E62" s="11"/>
       <c r="F62" s="26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G62" s="11"/>
       <c r="H62" s="11"/>
@@ -3316,7 +3332,7 @@
         <v>12</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D63" s="7">
         <f>1-0.005</f>
@@ -3335,7 +3351,7 @@
         <v>12</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D64" s="7">
         <f>1-0.005</f>
@@ -3351,17 +3367,17 @@
         <v>1</v>
       </c>
       <c r="B65" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C65" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="D65" s="7">
         <v>2.73</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="11"/>
@@ -3374,7 +3390,7 @@
         <v>12</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D66" s="7">
         <f>1-0.0035</f>
@@ -3393,7 +3409,7 @@
         <v>12</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D67" s="7">
         <f>1-0.0035</f>
@@ -3409,17 +3425,17 @@
         <v>1</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D68" s="25">
         <v>10</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="26" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="10"/>
@@ -3432,7 +3448,7 @@
         <v>12</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D69" s="25">
         <f>1-0.0035</f>
@@ -3451,7 +3467,7 @@
         <v>8</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -3467,14 +3483,14 @@
         <v>9</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="21"/>
       <c r="F71" s="20" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G71" s="20"/>
       <c r="H71" s="20"/>
@@ -3487,18 +3503,18 @@
         <v>9</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="21"/>
       <c r="F72" s="20" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G72" s="20"/>
       <c r="H72" s="20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -3509,14 +3525,14 @@
         <v>9</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="21"/>
       <c r="F73" s="20" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G73" s="20"/>
       <c r="H73" s="20"/>
@@ -3529,14 +3545,14 @@
         <v>9</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="21"/>
       <c r="F74" s="20" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G74" s="20"/>
       <c r="H74" s="20"/>
@@ -3558,7 +3574,7 @@
       <c r="F75" s="20"/>
       <c r="G75" s="20"/>
       <c r="H75" s="20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -3569,18 +3585,18 @@
         <v>9</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D76" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E76" s="21"/>
       <c r="F76" s="20" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G76" s="20"/>
       <c r="H76" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -3591,18 +3607,18 @@
         <v>9</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D77" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E77" s="21"/>
       <c r="F77" s="20" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G77" s="20"/>
       <c r="H77" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -3613,14 +3629,14 @@
         <v>9</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D78" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E78" s="21"/>
       <c r="F78" s="20" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G78" s="20"/>
       <c r="H78" s="21"/>
@@ -3633,14 +3649,14 @@
         <v>9</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D79" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E79" s="21"/>
       <c r="F79" s="20" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G79" s="20"/>
       <c r="H79" s="21"/>
@@ -3653,7 +3669,7 @@
         <v>12</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D80" s="19">
         <f>1-0.007</f>
@@ -3663,7 +3679,7 @@
       <c r="F80" s="20"/>
       <c r="G80" s="21"/>
       <c r="H80" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="81" spans="1:8" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3671,21 +3687,21 @@
         <v>1</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D81" s="19">
         <v>10</v>
       </c>
       <c r="E81" s="21"/>
       <c r="F81" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G81" s="21"/>
       <c r="H81" s="21" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="82" spans="1:8" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3696,7 +3712,7 @@
         <v>12</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D82" s="19">
         <f>1-0.007</f>
@@ -3715,7 +3731,7 @@
         <v>12</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D83" s="19">
         <f>1-0.007</f>
@@ -3731,17 +3747,17 @@
         <v>1</v>
       </c>
       <c r="B84" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C84" s="20" t="s">
         <v>111</v>
-      </c>
-      <c r="C84" s="20" t="s">
-        <v>113</v>
       </c>
       <c r="D84" s="19">
         <v>4</v>
       </c>
       <c r="E84" s="21"/>
       <c r="F84" s="20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G84" s="21"/>
       <c r="H84" s="21"/>
@@ -3754,7 +3770,7 @@
         <v>12</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D85" s="19">
         <f>1-0.007</f>
@@ -3773,7 +3789,7 @@
         <v>12</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D86" s="19">
         <f>1-0.007</f>
@@ -3789,17 +3805,17 @@
         <v>1</v>
       </c>
       <c r="B87" s="20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D87" s="19">
         <v>10</v>
       </c>
       <c r="E87" s="21"/>
       <c r="F87" s="20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G87" s="21"/>
       <c r="H87" s="20"/>
@@ -3812,7 +3828,7 @@
         <v>12</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D88" s="19">
         <f>1-0.007</f>
@@ -3831,7 +3847,7 @@
         <v>8</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
@@ -3865,18 +3881,18 @@
         <v>9</v>
       </c>
       <c r="C91" s="32" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D91" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E91" s="33"/>
       <c r="F91" s="33" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G91" s="29"/>
       <c r="H91" s="29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="92" spans="1:8" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3887,14 +3903,14 @@
         <v>9</v>
       </c>
       <c r="C92" s="32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D92" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E92" s="33"/>
       <c r="F92" s="33" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G92" s="29" t="s">
         <v>42</v>
@@ -3929,7 +3945,7 @@
         <v>8</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
@@ -3963,18 +3979,18 @@
         <v>9</v>
       </c>
       <c r="C96" s="32" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D96" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E96" s="33"/>
       <c r="F96" s="33" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G96" s="29"/>
       <c r="H96" s="29" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="97" spans="1:8" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3985,17 +4001,17 @@
         <v>9</v>
       </c>
       <c r="C97" s="32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D97" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E97" s="33"/>
       <c r="F97" s="33" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G97" s="29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H97" s="29"/>
     </row>
@@ -4025,7 +4041,7 @@
         <v>8</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
@@ -4041,7 +4057,7 @@
         <v>12</v>
       </c>
       <c r="C100" s="32" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D100" s="33">
         <v>0.85</v>
@@ -4050,7 +4066,7 @@
       <c r="F100" s="33"/>
       <c r="G100" s="29"/>
       <c r="H100" s="29" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:8" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4079,7 +4095,7 @@
         <v>8</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
@@ -4103,7 +4119,7 @@
       <c r="E103" s="33"/>
       <c r="F103" s="33"/>
       <c r="G103" s="29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H103" s="29" t="s">
         <v>45</v>
@@ -4117,7 +4133,7 @@
         <v>8</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
@@ -4130,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="B105" s="26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C105" s="26" t="s">
         <v>46</v>
@@ -4140,13 +4156,13 @@
       </c>
       <c r="E105" s="23"/>
       <c r="F105" s="26" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G105" s="26" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H105" s="26" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="106" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -4170,7 +4186,7 @@
         <v>48</v>
       </c>
       <c r="H106" s="26" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="107" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -4192,7 +4208,7 @@
       </c>
       <c r="G107" s="26"/>
       <c r="H107" s="26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -4203,7 +4219,7 @@
         <v>8</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
@@ -4216,7 +4232,7 @@
         <v>0</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C109" s="20" t="s">
         <v>46</v>
@@ -4226,13 +4242,13 @@
       </c>
       <c r="E109" s="21"/>
       <c r="F109" s="20" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H109" s="20" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="110" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -4240,7 +4256,7 @@
         <v>1</v>
       </c>
       <c r="B110" s="20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C110" s="20" t="s">
         <v>46</v>
@@ -4250,13 +4266,13 @@
       </c>
       <c r="E110" s="21"/>
       <c r="F110" s="20" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G110" s="20" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H110" s="20" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="111" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -4280,7 +4296,7 @@
         <v>48</v>
       </c>
       <c r="H111" s="20" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="112" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -4311,7 +4327,7 @@
         <v>8</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
@@ -4327,14 +4343,14 @@
         <v>9</v>
       </c>
       <c r="C114" s="26" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D114" s="34" t="s">
         <v>10</v>
       </c>
       <c r="E114" s="23"/>
       <c r="F114" s="23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G114" s="23"/>
       <c r="H114" s="26"/>
@@ -4347,14 +4363,14 @@
         <v>9</v>
       </c>
       <c r="C115" s="26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D115" s="25" t="s">
         <v>10</v>
       </c>
       <c r="E115" s="23"/>
       <c r="F115" s="23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G115" s="23"/>
       <c r="H115" s="26"/>
@@ -4367,14 +4383,14 @@
         <v>9</v>
       </c>
       <c r="C116" s="26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D116" s="25" t="s">
         <v>10</v>
       </c>
       <c r="E116" s="23"/>
       <c r="F116" s="23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G116" s="23"/>
       <c r="H116" s="26"/>
@@ -4398,47 +4414,51 @@
       <c r="H117" s="23"/>
     </row>
     <row r="118" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="25">
-        <v>1</v>
-      </c>
-      <c r="B118" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C118" s="26" t="s">
-        <v>50</v>
+      <c r="A118" s="49">
+        <v>1</v>
+      </c>
+      <c r="B118" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" s="50" t="s">
+        <v>177</v>
       </c>
       <c r="D118" s="25" t="s">
         <v>10</v>
       </c>
       <c r="E118" s="23"/>
       <c r="F118" s="23" t="s">
-        <v>52</v>
+        <v>178</v>
       </c>
       <c r="G118" s="23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H118" s="26" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
     </row>
     <row r="119" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B119" s="26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C119" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="D119" s="25">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="D119" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="E119" s="23"/>
-      <c r="F119" s="23"/>
-      <c r="G119" s="23"/>
+      <c r="F119" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="G119" s="23" t="s">
+        <v>58</v>
+      </c>
       <c r="H119" s="26" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
     </row>
     <row r="120" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -4446,41 +4466,39 @@
         <v>1</v>
       </c>
       <c r="B120" s="26" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C120" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D120" s="25" t="s">
-        <v>10</v>
+        <v>146</v>
+      </c>
+      <c r="D120" s="25">
+        <v>1</v>
       </c>
       <c r="E120" s="23"/>
-      <c r="F120" s="23" t="s">
-        <v>151</v>
-      </c>
+      <c r="F120" s="23"/>
       <c r="G120" s="23"/>
-      <c r="H120" s="24" t="s">
-        <v>157</v>
-      </c>
+      <c r="H120" s="26"/>
     </row>
     <row r="121" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="25">
         <v>1</v>
       </c>
       <c r="B121" s="26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C121" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="D121" s="25">
-        <v>0.95</v>
+        <v>50</v>
+      </c>
+      <c r="D121" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="E121" s="23"/>
-      <c r="F121" s="23"/>
+      <c r="F121" s="23" t="s">
+        <v>147</v>
+      </c>
       <c r="G121" s="23"/>
-      <c r="H121" s="24" t="s">
-        <v>160</v>
+      <c r="H121" s="26" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="122" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -4488,20 +4506,20 @@
         <v>1</v>
       </c>
       <c r="B122" s="26" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C122" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D122" s="25" t="s">
-        <v>10</v>
+        <v>153</v>
+      </c>
+      <c r="D122" s="25">
+        <v>0.95</v>
       </c>
       <c r="E122" s="23"/>
-      <c r="F122" s="23" t="s">
-        <v>59</v>
-      </c>
+      <c r="F122" s="23"/>
       <c r="G122" s="23"/>
-      <c r="H122" s="26"/>
+      <c r="H122" s="26" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="123" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="25">
@@ -4511,14 +4529,14 @@
         <v>9</v>
       </c>
       <c r="C123" s="26" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D123" s="25" t="s">
         <v>10</v>
       </c>
       <c r="E123" s="23"/>
       <c r="F123" s="23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G123" s="23"/>
       <c r="H123" s="26"/>
@@ -4531,14 +4549,14 @@
         <v>9</v>
       </c>
       <c r="C124" s="26" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D124" s="25" t="s">
         <v>10</v>
       </c>
       <c r="E124" s="23"/>
       <c r="F124" s="23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G124" s="23"/>
       <c r="H124" s="26"/>
@@ -4548,60 +4566,60 @@
         <v>1</v>
       </c>
       <c r="B125" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D125" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E125" s="23"/>
+      <c r="F125" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="G125" s="23"/>
+      <c r="H125" s="26"/>
+    </row>
+    <row r="126" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="25">
+        <v>1</v>
+      </c>
+      <c r="B126" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C125" s="26" t="s">
+      <c r="C126" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D125" s="48">
+      <c r="D126" s="48">
         <v>0.92</v>
       </c>
-      <c r="E125" s="23"/>
-      <c r="F125" s="26"/>
-      <c r="G125" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="H125" s="24" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="b">
+      <c r="E126" s="23"/>
+      <c r="F126" s="26"/>
+      <c r="G126" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="H126" s="24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B127" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C126" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D126" s="6"/>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-    </row>
-    <row r="127" spans="1:8" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="19">
-        <v>1</v>
-      </c>
-      <c r="B127" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C127" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D127" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="E127" s="21"/>
-      <c r="F127" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G127" s="21"/>
-      <c r="H127" s="20"/>
-    </row>
-    <row r="128" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C127" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D127" s="6"/>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="6"/>
+      <c r="H127" s="6"/>
+    </row>
+    <row r="128" spans="1:8" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="19">
         <v>1</v>
       </c>
@@ -4609,14 +4627,14 @@
         <v>9</v>
       </c>
       <c r="C128" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D128" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D128" s="35" t="s">
         <v>10</v>
       </c>
       <c r="E128" s="21"/>
       <c r="F128" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G128" s="21"/>
       <c r="H128" s="20"/>
@@ -4629,14 +4647,14 @@
         <v>9</v>
       </c>
       <c r="C129" s="20" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D129" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E129" s="21"/>
       <c r="F129" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G129" s="21"/>
       <c r="H129" s="20"/>
@@ -4646,82 +4664,84 @@
         <v>1</v>
       </c>
       <c r="B130" s="20" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C130" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D130" s="19">
-        <v>0.94</v>
+        <v>53</v>
+      </c>
+      <c r="D130" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="E130" s="21"/>
-      <c r="F130" s="20"/>
-      <c r="G130" s="20"/>
-      <c r="H130" s="21"/>
+      <c r="F130" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G130" s="21"/>
+      <c r="H130" s="20"/>
     </row>
     <row r="131" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="19">
         <v>1</v>
       </c>
       <c r="B131" s="20" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C131" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D131" s="19" t="s">
-        <v>10</v>
+        <v>49</v>
+      </c>
+      <c r="D131" s="19">
+        <v>0.94</v>
       </c>
       <c r="E131" s="21"/>
-      <c r="F131" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G131" s="21"/>
-      <c r="H131" s="20"/>
-    </row>
-    <row r="132" spans="1:8" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="19">
-        <v>1</v>
-      </c>
-      <c r="B132" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C132" s="20" t="s">
-        <v>51</v>
+      <c r="F131" s="20"/>
+      <c r="G131" s="20"/>
+      <c r="H131" s="21"/>
+    </row>
+    <row r="132" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="51">
+        <v>1</v>
+      </c>
+      <c r="B132" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="52" t="s">
+        <v>177</v>
       </c>
       <c r="D132" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E132" s="21"/>
       <c r="F132" s="21" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="G132" s="21"/>
       <c r="H132" s="20" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B133" s="20" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C133" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="D133" s="19">
-        <v>0.95</v>
+        <v>180</v>
+      </c>
+      <c r="D133" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="E133" s="21"/>
-      <c r="F133" s="21"/>
+      <c r="F133" s="21" t="s">
+        <v>181</v>
+      </c>
       <c r="G133" s="21"/>
       <c r="H133" s="20" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="19">
         <v>1</v>
       </c>
@@ -4729,37 +4749,39 @@
         <v>9</v>
       </c>
       <c r="C134" s="20" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D134" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E134" s="21"/>
       <c r="F134" s="21" t="s">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="G134" s="21"/>
-      <c r="H134" s="20"/>
-    </row>
-    <row r="135" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H134" s="20" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19">
         <v>1</v>
       </c>
       <c r="B135" s="20" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C135" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D135" s="19" t="s">
-        <v>10</v>
+        <v>153</v>
+      </c>
+      <c r="D135" s="19">
+        <v>0.95</v>
       </c>
       <c r="E135" s="21"/>
-      <c r="F135" s="21" t="s">
-        <v>59</v>
-      </c>
+      <c r="F135" s="21"/>
       <c r="G135" s="21"/>
-      <c r="H135" s="20"/>
+      <c r="H135" s="20" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="136" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="19">
@@ -4769,14 +4791,14 @@
         <v>9</v>
       </c>
       <c r="C136" s="20" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D136" s="19" t="s">
         <v>10</v>
       </c>
       <c r="E136" s="21"/>
       <c r="F136" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G136" s="21"/>
       <c r="H136" s="20"/>
@@ -4786,53 +4808,93 @@
         <v>1</v>
       </c>
       <c r="B137" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C137" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D137" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E137" s="21"/>
+      <c r="F137" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G137" s="21"/>
+      <c r="H137" s="20"/>
+    </row>
+    <row r="138" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="19">
+        <v>1</v>
+      </c>
+      <c r="B138" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D138" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E138" s="21"/>
+      <c r="F138" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G138" s="21"/>
+      <c r="H138" s="20"/>
+    </row>
+    <row r="139" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="19">
+        <v>1</v>
+      </c>
+      <c r="B139" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C137" s="20" t="s">
+      <c r="C139" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D137" s="48">
+      <c r="D139" s="48">
         <v>0.98</v>
       </c>
-      <c r="E137" s="21"/>
-      <c r="F137" s="20"/>
-      <c r="G137" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="H137" s="22" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
+      <c r="E139" s="21"/>
+      <c r="F139" s="20"/>
+      <c r="G139" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="H139" s="22" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C138" s="1" t="s">
+      <c r="B140" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="D140" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="E140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="F140" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G138" s="1" t="s">
+      <c r="G140" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H138" s="1" t="s">
+      <c r="H140" s="1" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G125" r:id="rId1" display="H4RG Options Summary" xr:uid="{C035A600-04E0-5A45-9DEB-9F1CAC882527}"/>
-    <hyperlink ref="G137" r:id="rId2" display="H4RG Options Summary" xr:uid="{0613B75C-56C8-6F48-B8E8-3ECD8427EBF5}"/>
+    <hyperlink ref="G126" r:id="rId1" display="H4RG Options Summary" xr:uid="{C035A600-04E0-5A45-9DEB-9F1CAC882527}"/>
+    <hyperlink ref="G139" r:id="rId2" display="H4RG Options Summary" xr:uid="{0613B75C-56C8-6F48-B8E8-3ECD8427EBF5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
